--- a/docs/mehanizmy-polya.xlsx
+++ b/docs/mehanizmy-polya.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Откуда поле" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Обзор'!$A$1:$G$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Поля по подгруппам'!$A$1:$H$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Обзор'!$A$1:$G$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Поля по подгруппам'!$A$1:$H$243</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Уточнения по типам'!$A$1:$J$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Откуда поле'!$A$1:$G$373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Откуда поле'!$A$1:$G$386</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1219,22 +1219,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь и хозяйственные принадлежности</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Встроенное и системное программное обеспечение</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1255,17 +1255,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1281,31 +1281,31 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>лист «Схема» (черновик)</t>
+          <t>лист «Классификатор»</t>
         </is>
       </c>
     </row>
@@ -1317,17 +1317,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1348,11 +1348,11 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>6</v>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>6</v>
@@ -1402,8 +1402,39 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>лист «Схема» (черновик)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G30"/>
+  <autoFilter ref="A1:G31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1414,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8278,12 +8309,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь и хозяйственные принадлежности</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Встроенное и системное программное обеспечение</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -8293,35 +8324,31 @@
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Вид</t>
+          <t>Наименование и версия ПО</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>выбор из списка</t>
+          <t>строка</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr"/>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>Производственный инвентарь; Хозяйственный инвентарь; Мелкие средства труда</t>
-        </is>
-      </c>
+      <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>inventoryKind</t>
+          <t>softName</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь и хозяйственные принадлежности</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Встроенное и системное программное обеспечение</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -8331,41 +8358,45 @@
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Материал</t>
+          <t>Способ использования</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>выбор из списка</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr"/>
-      <c r="G192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Лицензионное; Свободно распространяемое; Встроенное, неотчуждаемое от оборудования</t>
+        </is>
+      </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>licenseUse</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь и хозяйственные принадлежности</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Встроенное и системное программное обеспечение</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>дополнительные</t>
+          <t>основные</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Комплектность</t>
+          <t>Номер лицензии</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -8377,7 +8408,7 @@
       <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>kit</t>
+          <t>licenseNumber</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8420,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Встроенное и системное программное обеспечение</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -8399,23 +8430,19 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Вид</t>
+          <t>Оборудование (носитель), с которым ПО связано</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>выбор из списка</t>
+          <t>строка</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr"/>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t>Программное обеспечение; Лицензия; Прочее</t>
-        </is>
-      </c>
+      <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>intangibleKind</t>
+          <t>carrier</t>
         </is>
       </c>
     </row>
@@ -8427,29 +8454,33 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Встроенное и системное программное обеспечение</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Материальный носитель (оборудование)</t>
+          <t>Срок действия лицензии</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>выбор из списка</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr"/>
-      <c r="G195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Бессрочная; Ограниченная</t>
+        </is>
+      </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>carrier</t>
+          <t>licenseTerm</t>
         </is>
       </c>
     </row>
@@ -8461,29 +8492,29 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Встроенное и системное программное обеспечение</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Номер лицензии</t>
+          <t>Лицензия действует до</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>дата</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr"/>
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>licenseNumber</t>
+          <t>licenseUntil</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8526,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>— без подгрупп —</t>
+          <t>Встроенное и системное программное обеспечение</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -8505,31 +8536,35 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Лицензия действует до</t>
+          <t>Можно использовать или передать отдельно от оборудования</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>выбор из списка</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr"/>
-      <c r="G197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Да; Нет</t>
+        </is>
+      </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>licenseUntil</t>
+          <t>standalone</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -8539,7 +8574,7 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Марка (модель)</t>
+          <t>Наименование и версия ПО</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -8551,19 +8586,19 @@
       <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>softName</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -8573,31 +8608,35 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Заводской (серийный) номер</t>
+          <t>Тип лицензии</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>выбор из списка</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr"/>
-      <c r="G199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>На пользователя; На устройство; Серверная; Корпоративная; Подписка; Иная</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>serial</t>
+          <t>licenseKind</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -8607,7 +8646,7 @@
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Номер лицензии</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -8619,19 +8658,19 @@
       <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>maker</t>
+          <t>licenseNumber</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -8641,73 +8680,69 @@
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Управление</t>
+          <t>Количество пользователей / устройств</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>выбор из списка</t>
+          <t>целое число</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr"/>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>Ручное (универсальный); С ЧПУ; Полуавтоматическое</t>
-        </is>
-      </c>
+      <c r="G201" s="2" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>licenseSeats</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Мощность двигателя</t>
+          <t>Срок действия лицензии</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>кВт / л.с.</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="inlineStr"/>
+          <t>выбор из списка</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Бессрочная; Ограниченная</t>
+        </is>
+      </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>motorPower</t>
+          <t>licenseTerm</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -8717,35 +8752,31 @@
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Наибольшая длина обработки</t>
+          <t>Лицензия действует до</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F203" s="2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
+          <t>дата</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr"/>
       <c r="G203" s="2" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>workLength</t>
+          <t>licenseUntil</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -8755,35 +8786,31 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Наибольший диаметр (размер) обработки</t>
+          <t>Периодичность продления</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>мм</t>
-        </is>
-      </c>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr"/>
       <c r="G204" s="2" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>workSize</t>
+          <t>renewal</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -8793,69 +8820,69 @@
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Система ЧПУ</t>
+          <t>Техническая поддержка и обновления в рамках лицензии</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>выбор из списка</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Да; Нет</t>
+        </is>
+      </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>cncSystem</t>
+          <t>support</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>дополнительные</t>
+          <t>основные</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Масса</t>
+          <t>Наименование и назначение</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>кг / т</t>
-        </is>
-      </c>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>mass</t>
+          <t>dataPurpose</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -8865,31 +8892,35 @@
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Марка (модель)</t>
+          <t>Носитель хранения</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>выбор из списка</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Встроенная память оборудования; Отдельный сервер; Внешний носитель</t>
+        </is>
+      </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>dataStorage</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -8899,91 +8930,99 @@
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Уникальность</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>выбор из списка</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Разработано индивидуально под объект; Типовой продукт</t>
+        </is>
+      </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>maker</t>
+          <t>dataOrigin</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Выпускаемая продукция</t>
+          <t>Можно перенести на аналогичное оборудование</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>выбор из списка</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr"/>
-      <c r="G209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Да; Нет</t>
+        </is>
+      </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>portable</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Производительность</t>
+          <t>Есть резервная копия или документация по восстановлению</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="inlineStr">
-        <is>
-          <t>шт/ч / т/ч / м/мин</t>
-        </is>
-      </c>
-      <c r="G210" s="2" t="inlineStr"/>
+          <t>выбор из списка</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Да; Нет</t>
+        </is>
+      </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>productivity</t>
+          <t>backup</t>
         </is>
       </c>
     </row>
@@ -8995,7 +9034,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9005,19 +9044,19 @@
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Количество агрегатов в составе</t>
+          <t>Марка (модель)</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>целое число</t>
+          <t>строка</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="2" t="inlineStr"/>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>aggregates</t>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9068,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -9039,23 +9078,19 @@
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Установленная мощность</t>
+          <t>Заводской (серийный) номер</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F212" s="2" t="inlineStr">
-        <is>
-          <t>кВт</t>
-        </is>
-      </c>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr"/>
       <c r="G212" s="2" t="inlineStr"/>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>installedPower</t>
+          <t>serial</t>
         </is>
       </c>
     </row>
@@ -9067,33 +9102,29 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>дополнительные</t>
+          <t>основные</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Степень автоматизации</t>
+          <t>Производитель</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>выбор из списка</t>
+          <t>строка</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr"/>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>Ручная; Полуавтоматическая; Автоматическая</t>
-        </is>
-      </c>
+      <c r="G213" s="2" t="inlineStr"/>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>automation</t>
+          <t>maker</t>
         </is>
       </c>
     </row>
@@ -9105,33 +9136,33 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>дополнительные</t>
+          <t>основные</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Длина линии</t>
+          <t>Управление</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr"/>
+          <t>выбор из списка</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Ручное (универсальный); С ЧПУ; Полуавтоматическое</t>
+        </is>
+      </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>lineLength</t>
+          <t>control</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9174,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9153,19 +9184,23 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Марка (модель)</t>
+          <t>Мощность двигателя</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
-        </is>
-      </c>
-      <c r="F215" s="2" t="inlineStr"/>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>кВт / л.с.</t>
+        </is>
+      </c>
       <c r="G215" s="2" t="inlineStr"/>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>motorPower</t>
         </is>
       </c>
     </row>
@@ -9177,29 +9212,33 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Заводской (серийный) номер</t>
+          <t>Наибольшая длина обработки</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
-        </is>
-      </c>
-      <c r="F216" s="2" t="inlineStr"/>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>мм</t>
+        </is>
+      </c>
       <c r="G216" s="2" t="inlineStr"/>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>serial</t>
+          <t>workLength</t>
         </is>
       </c>
     </row>
@@ -9211,29 +9250,33 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Наибольший диаметр (размер) обработки</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
-        </is>
-      </c>
-      <c r="F217" s="2" t="inlineStr"/>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>мм</t>
+        </is>
+      </c>
       <c r="G217" s="2" t="inlineStr"/>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>maker</t>
+          <t>workSize</t>
         </is>
       </c>
     </row>
@@ -9245,33 +9288,29 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Рабочий объём</t>
+          <t>Система ЧПУ</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F218" s="2" t="inlineStr">
-        <is>
-          <t>л / м³</t>
-        </is>
-      </c>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>workVolume</t>
+          <t>cncSystem</t>
         </is>
       </c>
     </row>
@@ -9283,17 +9322,17 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Температура до</t>
+          <t>Масса</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -9303,13 +9342,13 @@
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>кг / т</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr"/>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>tempTo</t>
+          <t>mass</t>
         </is>
       </c>
     </row>
@@ -9321,7 +9360,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9331,23 +9370,19 @@
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Вид нагрева</t>
+          <t>Марка (модель)</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>выбор из списка</t>
+          <t>строка</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>Электрический; Газовый; Паровой; Без нагрева; Прочий</t>
-        </is>
-      </c>
+      <c r="G220" s="2" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>heating</t>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9359,33 +9394,29 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>дополнительные</t>
+          <t>основные</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Рабочее давление</t>
+          <t>Производитель</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr">
-        <is>
-          <t>МПа / бар</t>
-        </is>
-      </c>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr"/>
       <c r="G221" s="2" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>pressure</t>
+          <t>maker</t>
         </is>
       </c>
     </row>
@@ -9397,33 +9428,29 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>дополнительные</t>
+          <t>основные</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Материал</t>
+          <t>Выпускаемая продукция</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>выбор из списка</t>
+          <t>строка</t>
         </is>
       </c>
       <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t>Углеродистая сталь; Нержавеющая сталь; Эмалированная сталь; Прочее</t>
-        </is>
-      </c>
+      <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>vesselMaterial</t>
+          <t>product</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9462,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -9445,19 +9472,23 @@
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Марка (модель)</t>
+          <t>Производительность</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="inlineStr"/>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>шт/ч / т/ч / м/мин</t>
+        </is>
+      </c>
       <c r="G223" s="2" t="inlineStr"/>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>productivity</t>
         </is>
       </c>
     </row>
@@ -9469,7 +9500,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -9479,19 +9510,19 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Заводской (серийный) номер</t>
+          <t>Количество агрегатов в составе</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
+          <t>целое число</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr"/>
       <c r="G224" s="2" t="inlineStr"/>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>serial</t>
+          <t>aggregates</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9534,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -9513,19 +9544,23 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Установленная мощность</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>строка</t>
-        </is>
-      </c>
-      <c r="F225" s="2" t="inlineStr"/>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>кВт</t>
+        </is>
+      </c>
       <c r="G225" s="2" t="inlineStr"/>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>maker</t>
+          <t>installedPower</t>
         </is>
       </c>
     </row>
@@ -9537,33 +9572,33 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Производительность</t>
+          <t>Степень автоматизации</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>м³/ч / л/мин / м³/мин</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
+          <t>выбор из списка</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Ручная; Полуавтоматическая; Автоматическая</t>
+        </is>
+      </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>flow</t>
+          <t>automation</t>
         </is>
       </c>
     </row>
@@ -9575,17 +9610,17 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>основные</t>
+          <t>дополнительные</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Напор (давление)</t>
+          <t>Длина линии</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -9595,13 +9630,13 @@
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>м / МПа / бар / Па</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>lineLength</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9648,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -9623,23 +9658,19 @@
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Мощность двигателя</t>
+          <t>Марка (модель)</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>число</t>
-        </is>
-      </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>кВт / л.с.</t>
-        </is>
-      </c>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr"/>
       <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>motorPower</t>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9651,17 +9682,17 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>дополнительные</t>
+          <t>основные</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Рабочая среда</t>
+          <t>Заводской (серийный) номер</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -9673,7 +9704,7 @@
       <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>serial</t>
         </is>
       </c>
     </row>
@@ -9685,38 +9716,512 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr"/>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Рабочий объём</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>л / м³</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr"/>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>workVolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Температура до</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>tempTo</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Вид нагрева</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>выбор из списка</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Электрический; Газовый; Паровой; Без нагрева; Прочий</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>heating</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>дополнительные</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Рабочее давление</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>МПа / бар</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>дополнительные</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>выбор из списка</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Углеродистая сталь; Нержавеющая сталь; Эмалированная сталь; Прочее</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>vesselMaterial</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
           <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Марка (модель)</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Заводской (серийный) номер</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr"/>
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>м³/ч / л/мин / м³/мин</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Напор (давление)</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>м / МПа / бар / Па</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Мощность двигателя</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>кВт / л.с.</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>motorPower</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
         <is>
           <t>дополнительные</t>
         </is>
       </c>
-      <c r="D230" s="2" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Рабочая среда</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>дополнительные</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Число фаз</t>
         </is>
       </c>
-      <c r="E230" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>выбор из списка</t>
         </is>
       </c>
-      <c r="F230" s="2" t="inlineStr"/>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr">
         <is>
           <t>Однофазный; Трёхфазный</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>phases</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H230"/>
+  <autoFilter ref="A1:H243"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17266,7 +17771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G373"/>
+  <dimension ref="A1:G386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28734,87 +29239,99 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь и хозяйственные принадлежности</t>
-        </is>
-      </c>
-      <c r="B334" s="2" t="inlineStr"/>
+          <t>Нематериальные компоненты движимого имущества</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Встроенное и системное программное обеспечение</t>
+        </is>
+      </c>
       <c r="C334" s="2" t="inlineStr"/>
       <c r="D334" s="2" t="inlineStr">
         <is>
-          <t>Вид</t>
+          <t>Наименование и версия ПО</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Наименование и версия программного обеспечения</t>
         </is>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>inventoryKind</t>
+          <t>softName</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь и хозяйственные принадлежности</t>
-        </is>
-      </c>
-      <c r="B335" s="2" t="inlineStr"/>
+          <t>Нематериальные компоненты движимого имущества</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Встроенное и системное программное обеспечение</t>
+        </is>
+      </c>
       <c r="C335" s="2" t="inlineStr"/>
       <c r="D335" s="2" t="inlineStr">
         <is>
-          <t>Материал</t>
+          <t>Способ использования</t>
         </is>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Тип и номер лицензии (при наличии) / способ использования (лицензионное, свободно распространяемое, встроенное неотчуждаемое от оборудования)</t>
         </is>
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>licenseUse</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Инвентарь и хозяйственные принадлежности</t>
-        </is>
-      </c>
-      <c r="B336" s="2" t="inlineStr"/>
+          <t>Нематериальные компоненты движимого имущества</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Встроенное и системное программное обеспечение</t>
+        </is>
+      </c>
       <c r="C336" s="2" t="inlineStr"/>
       <c r="D336" s="2" t="inlineStr">
         <is>
-          <t>Комплектность</t>
+          <t>Номер лицензии</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Тип и номер лицензии (при наличии) / способ использования (лицензионное, свободно распространяемое, встроенное неотчуждаемое от оборудования)</t>
         </is>
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>kit</t>
+          <t>licenseNumber</t>
         </is>
       </c>
     </row>
@@ -28824,26 +29341,30 @@
           <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
-      <c r="B337" s="2" t="inlineStr"/>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Встроенное и системное программное обеспечение</t>
+        </is>
+      </c>
       <c r="C337" s="2" t="inlineStr"/>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Вид</t>
+          <t>Оборудование (носитель), с которым ПО связано</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Оборудование (носитель), с которым ПО функционально связано</t>
         </is>
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>intangibleKind</t>
+          <t>carrier</t>
         </is>
       </c>
     </row>
@@ -28853,26 +29374,30 @@
           <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
-      <c r="B338" s="2" t="inlineStr"/>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Встроенное и системное программное обеспечение</t>
+        </is>
+      </c>
       <c r="C338" s="2" t="inlineStr"/>
       <c r="D338" s="2" t="inlineStr">
         <is>
-          <t>Материальный носитель (оборудование)</t>
+          <t>Срок действия лицензии</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Срок действия лицензии (бессрочная/ограниченная, дата окончания)</t>
         </is>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>carrier</t>
+          <t>licenseTerm</t>
         </is>
       </c>
     </row>
@@ -28882,26 +29407,30 @@
           <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
-      <c r="B339" s="2" t="inlineStr"/>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Встроенное и системное программное обеспечение</t>
+        </is>
+      </c>
       <c r="C339" s="2" t="inlineStr"/>
       <c r="D339" s="2" t="inlineStr">
         <is>
-          <t>Номер лицензии</t>
+          <t>Лицензия действует до</t>
         </is>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Срок действия лицензии (бессрочная/ограниченная, дата окончания)</t>
         </is>
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>licenseNumber</t>
+          <t>licenseUntil</t>
         </is>
       </c>
     </row>
@@ -28911,455 +29440,459 @@
           <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
-      <c r="B340" s="2" t="inlineStr"/>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Встроенное и системное программное обеспечение</t>
+        </is>
+      </c>
       <c r="C340" s="2" t="inlineStr"/>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Лицензия действует до</t>
+          <t>Можно использовать или передать отдельно от оборудования</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Возможность автономного использования/передачи отдельно от оборудования</t>
         </is>
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>licenseUntil</t>
+          <t>standalone</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr"/>
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>Марка (модель)</t>
+          <t>Наименование и версия ПО</t>
         </is>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Наименование и версия программного обеспечения</t>
         </is>
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>softName</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr"/>
       <c r="D342" s="2" t="inlineStr">
         <is>
-          <t>Заводской (серийный) номер</t>
+          <t>Тип лицензии</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Тип и номер лицензии (per-user, per-device, серверная, корпоративная и т.д.)</t>
         </is>
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>serial</t>
+          <t>licenseKind</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr"/>
       <c r="D343" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Номер лицензии</t>
         </is>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Тип и номер лицензии (per-user, per-device, серверная, корпоративная и т.д.)</t>
         </is>
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>maker</t>
+          <t>licenseNumber</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr"/>
       <c r="D344" s="2" t="inlineStr">
         <is>
-          <t>Управление</t>
+          <t>Количество пользователей / устройств</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Количество лицензированных пользователей/устройств (если применимо)</t>
         </is>
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>licenseSeats</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr"/>
       <c r="D345" s="2" t="inlineStr">
         <is>
-          <t>Мощность двигателя</t>
+          <t>Срок действия лицензии</t>
         </is>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Срок действия лицензии / периодичность продления (для подписочных моделей)</t>
         </is>
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>motorPower</t>
+          <t>licenseTerm</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr"/>
       <c r="D346" s="2" t="inlineStr">
         <is>
-          <t>Наибольшая длина обработки</t>
+          <t>Лицензия действует до</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Срок действия лицензии / периодичность продления (для подписочных моделей)</t>
         </is>
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>workLength</t>
+          <t>licenseUntil</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr"/>
       <c r="D347" s="2" t="inlineStr">
         <is>
-          <t>Наибольший диаметр (размер) обработки</t>
+          <t>Периодичность продления</t>
         </is>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Срок действия лицензии / периодичность продления (для подписочных моделей)</t>
         </is>
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>workSize</t>
+          <t>renewal</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Прикладное программное обеспечение и цифровые лицензии</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr"/>
       <c r="D348" s="2" t="inlineStr">
         <is>
-          <t>Система ЧПУ</t>
+          <t>Техническая поддержка и обновления в рамках лицензии</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Наличие технической поддержки/обновлений в рамках лицензии</t>
         </is>
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>cncSystem</t>
+          <t>support</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Станки и обрабатывающие центры</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr"/>
       <c r="D349" s="2" t="inlineStr">
         <is>
-          <t>Масса</t>
+          <t>Наименование и назначение</t>
         </is>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F349" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Наименование и назначение (для какого оборудования/процесса разработано)</t>
         </is>
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>mass</t>
+          <t>dataPurpose</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr"/>
       <c r="D350" s="2" t="inlineStr">
         <is>
-          <t>Марка (модель)</t>
+          <t>Носитель хранения</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Носитель хранения (встроенная память оборудования, отдельный сервер, внешний носитель)</t>
         </is>
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>dataStorage</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr"/>
       <c r="D351" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Уникальность</t>
         </is>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F351" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Уникальность/оригинальность (разработано индивидуально под объект либо является типовым продуктом)</t>
         </is>
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>maker</t>
+          <t>dataOrigin</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr"/>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Выпускаемая продукция</t>
+          <t>Можно перенести на аналогичное оборудование</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Возможность переноса на аналогичное оборудование</t>
         </is>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>portable</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>Технологическое (производственное) оборудование</t>
+          <t>Нематериальные компоненты движимого имущества</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Технологические базы данных и конфигурации</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr"/>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Производительность</t>
+          <t>Есть резервная копия или документация по восстановлению</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
-          <t>со схемы</t>
+          <t>параметр таблицы</t>
         </is>
       </c>
       <c r="F353" s="2" t="inlineStr">
         <is>
-          <t>класса нет на листе «Классификатор»</t>
+          <t>Наличие резервной копии / документации по восстановлению</t>
         </is>
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>productivity</t>
+          <t>backup</t>
         </is>
       </c>
     </row>
@@ -29371,13 +29904,13 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr"/>
       <c r="D354" s="2" t="inlineStr">
         <is>
-          <t>Количество агрегатов в составе</t>
+          <t>Марка (модель)</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -29392,7 +29925,7 @@
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>aggregates</t>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -29404,13 +29937,13 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr"/>
       <c r="D355" s="2" t="inlineStr">
         <is>
-          <t>Установленная мощность</t>
+          <t>Заводской (серийный) номер</t>
         </is>
       </c>
       <c r="E355" s="2" t="inlineStr">
@@ -29425,7 +29958,7 @@
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>installedPower</t>
+          <t>serial</t>
         </is>
       </c>
     </row>
@@ -29437,13 +29970,13 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr"/>
       <c r="D356" s="2" t="inlineStr">
         <is>
-          <t>Степень автоматизации</t>
+          <t>Производитель</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -29458,7 +29991,7 @@
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>automation</t>
+          <t>maker</t>
         </is>
       </c>
     </row>
@@ -29470,13 +30003,13 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>Технологические линии и их составные агрегаты</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr"/>
       <c r="D357" s="2" t="inlineStr">
         <is>
-          <t>Длина линии</t>
+          <t>Управление</t>
         </is>
       </c>
       <c r="E357" s="2" t="inlineStr">
@@ -29491,7 +30024,7 @@
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>lineLength</t>
+          <t>control</t>
         </is>
       </c>
     </row>
@@ -29503,13 +30036,13 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr"/>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Марка (модель)</t>
+          <t>Мощность двигателя</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -29524,7 +30057,7 @@
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>motorPower</t>
         </is>
       </c>
     </row>
@@ -29536,13 +30069,13 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr"/>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Заводской (серийный) номер</t>
+          <t>Наибольшая длина обработки</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -29557,7 +30090,7 @@
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>serial</t>
+          <t>workLength</t>
         </is>
       </c>
     </row>
@@ -29569,13 +30102,13 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr"/>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Наибольший диаметр (размер) обработки</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -29590,7 +30123,7 @@
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>maker</t>
+          <t>workSize</t>
         </is>
       </c>
     </row>
@@ -29602,13 +30135,13 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr"/>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Рабочий объём</t>
+          <t>Система ЧПУ</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -29623,7 +30156,7 @@
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>workVolume</t>
+          <t>cncSystem</t>
         </is>
       </c>
     </row>
@@ -29635,13 +30168,13 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Станки и обрабатывающие центры</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr"/>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Температура до</t>
+          <t>Масса</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -29656,7 +30189,7 @@
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>tempTo</t>
+          <t>mass</t>
         </is>
       </c>
     </row>
@@ -29668,13 +30201,13 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr"/>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Вид нагрева</t>
+          <t>Марка (модель)</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -29689,7 +30222,7 @@
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>heating</t>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -29701,13 +30234,13 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr"/>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Рабочее давление</t>
+          <t>Производитель</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -29722,7 +30255,7 @@
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>pressure</t>
+          <t>maker</t>
         </is>
       </c>
     </row>
@@ -29734,13 +30267,13 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr"/>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Материал</t>
+          <t>Выпускаемая продукция</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -29755,7 +30288,7 @@
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>vesselMaterial</t>
+          <t>product</t>
         </is>
       </c>
     </row>
@@ -29767,13 +30300,13 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr"/>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Марка (модель)</t>
+          <t>Производительность</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -29788,7 +30321,7 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>productivity</t>
         </is>
       </c>
     </row>
@@ -29800,13 +30333,13 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr"/>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Заводской (серийный) номер</t>
+          <t>Количество агрегатов в составе</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -29821,7 +30354,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>serial</t>
+          <t>aggregates</t>
         </is>
       </c>
     </row>
@@ -29833,13 +30366,13 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr"/>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Производитель</t>
+          <t>Установленная мощность</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -29854,7 +30387,7 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>maker</t>
+          <t>installedPower</t>
         </is>
       </c>
     </row>
@@ -29866,13 +30399,13 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr"/>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Производительность</t>
+          <t>Степень автоматизации</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -29887,7 +30420,7 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>flow</t>
+          <t>automation</t>
         </is>
       </c>
     </row>
@@ -29899,13 +30432,13 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Технологические линии и их составные агрегаты</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr"/>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Напор (давление)</t>
+          <t>Длина линии</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -29920,7 +30453,7 @@
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>lineLength</t>
         </is>
       </c>
     </row>
@@ -29932,13 +30465,13 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr"/>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Мощность двигателя</t>
+          <t>Марка (модель)</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -29953,7 +30486,7 @@
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>motorPower</t>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -29965,13 +30498,13 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr"/>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Рабочая среда</t>
+          <t>Заводской (серийный) номер</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -29986,7 +30519,7 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>serial</t>
         </is>
       </c>
     </row>
@@ -29998,33 +30531,462 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr"/>
       <c r="D373" s="2" t="inlineStr">
         <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr"/>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Рабочий объём</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>workVolume</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr"/>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Температура до</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>tempTo</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr"/>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Вид нагрева</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>heating</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr"/>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Рабочее давление</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Печи, сушильные камеры, реакторы, ёмкости технологического назначения</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr"/>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Материал</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>vesselMaterial</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr"/>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Марка (модель)</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr"/>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Заводской (серийный) номер</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr"/>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr"/>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Производительность</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr"/>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Напор (давление)</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>head</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr"/>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Мощность двигателя</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>motorPower</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr"/>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Рабочая среда</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Технологическое (производственное) оборудование</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Насосное, компрессорное, вентиляционное оборудование производственного назначения</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr"/>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
           <t>Число фаз</t>
         </is>
       </c>
-      <c r="E373" s="2" t="inlineStr">
+      <c r="E386" s="2" t="inlineStr">
         <is>
           <t>со схемы</t>
         </is>
       </c>
-      <c r="F373" s="2" t="inlineStr">
+      <c r="F386" s="2" t="inlineStr">
         <is>
           <t>класса нет на листе «Классификатор»</t>
         </is>
       </c>
-      <c r="G373" s="2" t="inlineStr">
+      <c r="G386" s="2" t="inlineStr">
         <is>
           <t>phases</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G373"/>
+  <autoFilter ref="A1:G386"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/mehanizmy-polya.xlsx
+++ b/docs/mehanizmy-polya.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Откуда поле" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Обзор'!$A$1:$G$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Поля по подгруппам'!$A$1:$H$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Обзор'!$A$1:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Поля по подгруппам'!$A$1:$H$250</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Уточнения по типам'!$A$1:$J$165</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Откуда поле'!$A$1:$G$386</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Откуда поле'!$A$1:$G$393</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1433,8 +1433,39 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>— без подгрупп —</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>лист «Классификатор»</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G31"/>
+  <autoFilter ref="A1:G32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1445,7 +1476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10220,8 +10251,254 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>— без подгрупп —</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Вид</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>выбор из списка</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr"/>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Навесное оборудование; Прицепное оборудование; Оросительное оборудование; Прочее</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>otherKind</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>— без подгрупп —</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Марка (модель)</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>— без подгрупп —</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Заводской (серийный) номер</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr"/>
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>— без подгрупп —</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>— без подгрупп —</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>основные</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>С чем работает</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr"/>
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>worksWith</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>— без подгрупп —</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>дополнительные</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Масса</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>число</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>кг / т</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>— без подгрупп —</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>дополнительные</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Комплектность</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>строка</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr"/>
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H243"/>
+  <autoFilter ref="A1:H250"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17771,7 +18048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G386"/>
+  <dimension ref="A1:G393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -30985,8 +31262,211 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr"/>
+      <c r="C387" s="2" t="inlineStr"/>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Вид</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>otherKind</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr"/>
+      <c r="C388" s="2" t="inlineStr"/>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Марка (модель)</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr"/>
+      <c r="C389" s="2" t="inlineStr"/>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Заводской (серийный) номер</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr"/>
+      <c r="C390" s="2" t="inlineStr"/>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Производитель</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>maker</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr"/>
+      <c r="C391" s="2" t="inlineStr"/>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>С чем работает</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>worksWith</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr"/>
+      <c r="C392" s="2" t="inlineStr"/>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Масса</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>mass</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr"/>
+      <c r="C393" s="2" t="inlineStr"/>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Комплектность</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>со схемы</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>класса нет на листе «Классификатор»</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G386"/>
+  <autoFilter ref="A1:G393"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/mehanizmy-polya.xlsx
+++ b/docs/mehanizmy-polya.xlsx
@@ -8461,7 +8461,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Оборудование (носитель), с которым ПО связано</t>
+          <t>Оборудование — носитель ПО</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Можно использовать или передать отдельно от оборудования</t>
+          <t>Автономное использование и передача отдельно от оборудования</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Можно перенести на аналогичное оборудование</t>
+          <t>Перенос на аналогичное оборудование</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Есть резервная копия или документация по восстановлению</t>
+          <t>Резервная копия или документация по восстановлению</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>С чем работает</t>
+          <t>Базовая машина (агрегат)</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       <c r="G248" s="2" t="inlineStr"/>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>worksWith</t>
+          <t>baseMachine</t>
         </is>
       </c>
     </row>
@@ -29626,7 +29626,7 @@
       <c r="C337" s="2" t="inlineStr"/>
       <c r="D337" s="2" t="inlineStr">
         <is>
-          <t>Оборудование (носитель), с которым ПО связано</t>
+          <t>Оборудование — носитель ПО</t>
         </is>
       </c>
       <c r="E337" s="2" t="inlineStr">
@@ -29725,7 +29725,7 @@
       <c r="C340" s="2" t="inlineStr"/>
       <c r="D340" s="2" t="inlineStr">
         <is>
-          <t>Можно использовать или передать отдельно от оборудования</t>
+          <t>Автономное использование и передача отдельно от оборудования</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -30121,7 +30121,7 @@
       <c r="C352" s="2" t="inlineStr"/>
       <c r="D352" s="2" t="inlineStr">
         <is>
-          <t>Можно перенести на аналогичное оборудование</t>
+          <t>Перенос на аналогичное оборудование</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -30154,7 +30154,7 @@
       <c r="C353" s="2" t="inlineStr"/>
       <c r="D353" s="2" t="inlineStr">
         <is>
-          <t>Есть резервная копия или документация по восстановлению</t>
+          <t>Резервная копия или документация по восстановлению</t>
         </is>
       </c>
       <c r="E353" s="2" t="inlineStr">
@@ -31388,7 +31388,7 @@
       <c r="C391" s="2" t="inlineStr"/>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>С чем работает</t>
+          <t>Базовая машина (агрегат)</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -31403,7 +31403,7 @@
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>worksWith</t>
+          <t>baseMachine</t>
         </is>
       </c>
     </row>
